--- a/data/trans_camb/P0901-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P0901-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 11,01</t>
+          <t>4,45; 11,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,65</t>
+          <t>2,03; 9,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 17,39</t>
+          <t>8,34; 17,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 14,53</t>
+          <t>7,25; 14,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,76; 14,84</t>
+          <t>6,42; 14,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,59; 20,84</t>
+          <t>13,54; 21,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 12,05</t>
+          <t>7,08; 12,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 11,59</t>
+          <t>5,75; 11,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,12; 18,66</t>
+          <t>12,87; 18,66</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,45; 68,88</t>
+          <t>23,02; 73,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,47; 60,71</t>
+          <t>10,43; 61,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,04; 110,16</t>
+          <t>44,12; 108,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,61; 59,1</t>
+          <t>25,49; 57,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,22; 61,13</t>
+          <t>23,0; 59,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,28; 83,87</t>
+          <t>48,83; 85,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,03; 56,49</t>
+          <t>30,59; 59,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,57; 54,31</t>
+          <t>24,45; 52,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55,6; 87,53</t>
+          <t>54,42; 88,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,05</t>
+          <t>-0,14; 3,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,18</t>
+          <t>-0,02; 3,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,3</t>
+          <t>1,54; 7,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,62</t>
+          <t>-0,54; 3,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,53</t>
+          <t>1,08; 5,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 5,73</t>
+          <t>-0,54; 5,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,89</t>
+          <t>0,08; 2,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,8</t>
+          <t>1,08; 3,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,01</t>
+          <t>1,76; 6,13</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 63,41</t>
+          <t>-3,36; 62,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 66,61</t>
+          <t>0,15; 67,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,59; 143,48</t>
+          <t>28,53; 145,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 40,03</t>
+          <t>-4,96; 43,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,35; 61,62</t>
+          <t>9,69; 59,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 62,36</t>
+          <t>-4,67; 61,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 41,99</t>
+          <t>1,0; 40,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,52; 54,11</t>
+          <t>13,18; 53,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,44; 82,36</t>
+          <t>21,84; 84,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 5,19</t>
+          <t>-1,2; 5,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,81</t>
+          <t>-1,71; 3,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 6,19</t>
+          <t>0,59; 6,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 2,47</t>
+          <t>-4,78; 2,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 4,97</t>
+          <t>-3,08; 4,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 3,66</t>
+          <t>-2,89; 3,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,94</t>
+          <t>-1,67; 3,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,65</t>
+          <t>-1,24; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,11</t>
+          <t>-0,07; 4,27</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 152,92</t>
+          <t>-20,85; 160,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 121,78</t>
+          <t>-30,39; 126,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,86; 190,02</t>
+          <t>8,56; 198,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,65; 39,27</t>
+          <t>-44,53; 37,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 69,29</t>
+          <t>-28,59; 73,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 54,38</t>
+          <t>-25,24; 50,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 55,28</t>
+          <t>-22,31; 60,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 64,7</t>
+          <t>-15,19; 61,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 75,12</t>
+          <t>-1,54; 78,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,58</t>
+          <t>1,51; 4,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,97</t>
+          <t>0,04; 2,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,86</t>
+          <t>0,77; 5,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,49</t>
+          <t>2,64; 6,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,77</t>
+          <t>1,23; 4,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,6</t>
+          <t>-0,98; 4,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,01</t>
+          <t>2,49; 4,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,57</t>
+          <t>1,15; 3,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,81</t>
+          <t>1,05; 4,84</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,0; 55,72</t>
+          <t>15,3; 54,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 35,42</t>
+          <t>-0,2; 34,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,4; 69,35</t>
+          <t>11,72; 69,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,71; 41,9</t>
+          <t>15,02; 40,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,39; 31,06</t>
+          <t>7,37; 32,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 29,53</t>
+          <t>-4,59; 30,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,18; 41,15</t>
+          <t>18,78; 40,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,42; 29,43</t>
+          <t>8,78; 29,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,11; 38,92</t>
+          <t>8,13; 38,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P0901-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P0901-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,67</t>
+          <t>11,27</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,34</t>
+          <t>16,79</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15,76</t>
+          <t>14,76</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,48</t>
+          <t>4,23; 11,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,83</t>
+          <t>2,01; 9,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,34; 17,41</t>
+          <t>6,99; 15,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 14,26</t>
+          <t>7,08; 14,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 14,95</t>
+          <t>6,32; 14,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,54; 21,06</t>
+          <t>13,04; 20,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 12,45</t>
+          <t>7,03; 12,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 11,41</t>
+          <t>5,59; 11,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,87; 18,66</t>
+          <t>12,1; 17,58</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>65,92%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,02; 73,39</t>
+          <t>22,24; 75,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,43; 61,24</t>
+          <t>10,22; 64,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,12; 108,57</t>
+          <t>36,52; 101,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,49; 57,94</t>
+          <t>24,39; 58,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,0; 59,78</t>
+          <t>22,71; 57,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,83; 85,7</t>
+          <t>45,06; 82,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,59; 59,36</t>
+          <t>29,61; 57,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,45; 52,58</t>
+          <t>23,85; 52,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,42; 88,29</t>
+          <t>51,37; 83,93</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>6,18</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>5,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,09</t>
+          <t>-0,02; 3,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,26</t>
+          <t>0,22; 3,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,13</t>
+          <t>4,39; 7,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,89</t>
+          <t>-0,63; 3,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,32</t>
+          <t>1,0; 5,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,83</t>
+          <t>3,3; 7,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,81</t>
+          <t>0,13; 2,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,81</t>
+          <t>1,08; 3,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,13</t>
+          <t>4,4; 7,17</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>111,17%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 62,67</t>
+          <t>0,6; 65,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 67,84</t>
+          <t>3,13; 74,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,53; 145,69</t>
+          <t>68,39; 170,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 43,06</t>
+          <t>-5,73; 42,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 59,43</t>
+          <t>7,8; 57,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 61,93</t>
+          <t>28,52; 83,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 40,24</t>
+          <t>1,56; 40,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,18; 53,59</t>
+          <t>12,73; 52,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,84; 84,51</t>
+          <t>52,99; 101,99</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>2,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 5,09</t>
+          <t>-0,99; 5,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,97</t>
+          <t>-1,69; 3,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,17</t>
+          <t>0,66; 5,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 2,77</t>
+          <t>-4,87; 2,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 4,96</t>
+          <t>-2,73; 4,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 3,54</t>
+          <t>-2,45; 4,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,2</t>
+          <t>-1,88; 2,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 3,44</t>
+          <t>-1,04; 3,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,27</t>
+          <t>0,14; 4,52</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 160,11</t>
+          <t>-20,31; 144,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 126,87</t>
+          <t>-31,36; 120,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,56; 198,9</t>
+          <t>10,33; 182,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,53; 37,59</t>
+          <t>-45,23; 35,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,59; 73,23</t>
+          <t>-24,98; 70,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 50,66</t>
+          <t>-21,59; 62,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 60,3</t>
+          <t>-24,91; 54,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 61,07</t>
+          <t>-15,16; 59,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 78,55</t>
+          <t>1,37; 82,61</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>4,62</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,32</t>
+          <t>4,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,52</t>
+          <t>1,44; 4,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,93</t>
+          <t>-0,1; 2,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,69</t>
+          <t>3,0; 6,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,2</t>
+          <t>2,72; 6,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,95</t>
+          <t>1,26; 4,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,78</t>
+          <t>2,58; 5,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,95</t>
+          <t>2,6; 4,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,57</t>
+          <t>0,92; 3,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,84</t>
+          <t>3,49; 5,73</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,3; 54,22</t>
+          <t>14,28; 55,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 34,5</t>
+          <t>-1,03; 34,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,72; 69,19</t>
+          <t>30,28; 71,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,02; 40,43</t>
+          <t>15,55; 41,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,37; 32,27</t>
+          <t>7,19; 31,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 30,63</t>
+          <t>14,69; 38,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,78; 40,98</t>
+          <t>19,65; 40,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,78; 29,35</t>
+          <t>6,87; 28,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,13; 38,99</t>
+          <t>25,95; 47,13</t>
         </is>
       </c>
     </row>
